--- a/data/base_rede_brasil.xlsx
+++ b/data/base_rede_brasil.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olostec-my.sharepoint.com/personal/gerber_souza_olos_com_br/Documents/1 - Painel/Python/Cockpit/OSPDataCommandCenter_GitHub_Atualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC9E8A6-9B4D-4E52-9532-4F706545A0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{3CC9E8A6-9B4D-4E52-9532-4F706545A0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD6A810-F915-4B74-97C6-1228211587D5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C00F07DC-FCAD-41EA-B97E-6D567717E76C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C00F07DC-FCAD-41EA-B97E-6D567717E76C}"/>
   </bookViews>
   <sheets>
     <sheet name="Locator" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="37">
   <si>
     <t>Data</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D79DB9-BC20-4CEF-B5A7-6EE2B6ECC936}">
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5209,49 +5209,191 @@
         <v>10</v>
       </c>
       <c r="I67">
-        <v>361796</v>
+        <v>362322</v>
       </c>
       <c r="J67">
-        <v>956</v>
+        <v>1450</v>
       </c>
       <c r="K67">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O67" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P67" s="2">
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R67" s="3">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" s="3">
+        <v>0</v>
+      </c>
+      <c r="V67" s="3">
+        <v>0.92449999999999999</v>
+      </c>
+      <c r="W67">
+        <v>120.2941</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B68">
+        <v>16</v>
+      </c>
+      <c r="C68">
+        <v>988</v>
+      </c>
+      <c r="D68">
+        <v>990</v>
+      </c>
+      <c r="E68" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68">
+        <v>60158</v>
+      </c>
+      <c r="G68">
+        <v>255</v>
+      </c>
+      <c r="H68">
+        <v>7</v>
+      </c>
+      <c r="I68">
+        <v>218230</v>
+      </c>
+      <c r="J68">
+        <v>421</v>
+      </c>
+      <c r="K68">
+        <v>17</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>17</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2">
         <v>2.199074074074074E-4</v>
       </c>
-      <c r="P67" s="2">
-        <v>2.0370370370370369E-3</v>
-      </c>
-      <c r="Q67" s="3">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R67" s="3">
-        <v>3.0300000000000001E-2</v>
-      </c>
-      <c r="S67" s="3">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67" s="3">
-        <v>0</v>
-      </c>
-      <c r="V67" s="3">
-        <v>0.97729999999999995</v>
-      </c>
-      <c r="W67">
-        <v>117.6187</v>
+      <c r="P68" s="2">
+        <v>1.8518518518518519E-3</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="R68" s="3">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0.75609999999999999</v>
+      </c>
+      <c r="W68">
+        <v>64.2166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B69">
+        <v>17</v>
+      </c>
+      <c r="C69">
+        <v>988</v>
+      </c>
+      <c r="D69">
+        <v>990</v>
+      </c>
+      <c r="E69" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69">
+        <v>60158</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>126</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" t="s">
+        <v>25</v>
+      </c>
+      <c r="S69" t="s">
+        <v>25</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69" t="s">
+        <v>25</v>
+      </c>
+      <c r="V69" t="s">
+        <v>25</v>
+      </c>
+      <c r="W69">
+        <v>3.9E-2</v>
       </c>
     </row>
   </sheetData>
